--- a/07_Final_Output/Final_KTU_Results.xlsx
+++ b/07_Final_Output/Final_KTU_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="225">
   <si>
     <t>AIL202</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>Supply</t>
   </si>
   <si>
     <t>HUT200, MCN202</t>
@@ -1062,6 +1065,7 @@
   <dimension ref="A1:S155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
     <col min="19" max="19" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1176,8 +1180,8 @@
       <c r="Q2" t="s">
         <v>173</v>
       </c>
-      <c r="R2">
-        <v>0</v>
+      <c r="R2" t="s">
+        <v>186</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>3</v>
@@ -1235,8 +1239,8 @@
       <c r="Q3" t="s">
         <v>173</v>
       </c>
-      <c r="R3">
-        <v>0</v>
+      <c r="R3" t="s">
+        <v>186</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>13</v>
@@ -1294,8 +1298,8 @@
       <c r="Q4" t="s">
         <v>173</v>
       </c>
-      <c r="R4">
-        <v>5.5</v>
+      <c r="R4" t="s">
+        <v>186</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>173</v>
@@ -1353,8 +1357,8 @@
       <c r="Q5" t="s">
         <v>173</v>
       </c>
-      <c r="R5">
-        <v>7</v>
+      <c r="R5" t="s">
+        <v>186</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>173</v>
@@ -1412,11 +1416,11 @@
       <c r="Q6" t="s">
         <v>185</v>
       </c>
-      <c r="R6">
-        <v>4.8</v>
+      <c r="R6" t="s">
+        <v>186</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1471,11 +1475,11 @@
       <c r="Q7" t="s">
         <v>173</v>
       </c>
-      <c r="R7">
-        <v>0</v>
+      <c r="R7" t="s">
+        <v>186</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1530,8 +1534,8 @@
       <c r="Q8" t="s">
         <v>173</v>
       </c>
-      <c r="R8">
-        <v>5.5</v>
+      <c r="R8" t="s">
+        <v>186</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>173</v>
@@ -1589,8 +1593,8 @@
       <c r="Q9" t="s">
         <v>173</v>
       </c>
-      <c r="R9">
-        <v>3.5</v>
+      <c r="R9" t="s">
+        <v>186</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>13</v>
@@ -1648,11 +1652,11 @@
       <c r="Q10" t="s">
         <v>185</v>
       </c>
-      <c r="R10">
-        <v>0</v>
+      <c r="R10" t="s">
+        <v>186</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1707,8 +1711,8 @@
       <c r="Q11" t="s">
         <v>173</v>
       </c>
-      <c r="R11">
-        <v>2.75</v>
+      <c r="R11" t="s">
+        <v>186</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>4</v>
@@ -1766,8 +1770,8 @@
       <c r="Q12" t="s">
         <v>173</v>
       </c>
-      <c r="R12">
-        <v>6.5</v>
+      <c r="R12" t="s">
+        <v>186</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>173</v>
@@ -1825,11 +1829,11 @@
       <c r="Q13" t="s">
         <v>183</v>
       </c>
-      <c r="R13">
-        <v>0</v>
+      <c r="R13" t="s">
+        <v>186</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1884,8 +1888,8 @@
       <c r="Q14" t="s">
         <v>173</v>
       </c>
-      <c r="R14">
-        <v>0</v>
+      <c r="R14" t="s">
+        <v>186</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>4</v>
@@ -1943,8 +1947,8 @@
       <c r="Q15" t="s">
         <v>173</v>
       </c>
-      <c r="R15">
-        <v>5.5</v>
+      <c r="R15" t="s">
+        <v>186</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>173</v>
@@ -2002,8 +2006,8 @@
       <c r="Q16" t="s">
         <v>173</v>
       </c>
-      <c r="R16">
-        <v>6</v>
+      <c r="R16" t="s">
+        <v>186</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>14</v>
@@ -2061,8 +2065,8 @@
       <c r="Q17" t="s">
         <v>173</v>
       </c>
-      <c r="R17">
-        <v>5.5</v>
+      <c r="R17" t="s">
+        <v>186</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>14</v>
@@ -2120,11 +2124,11 @@
       <c r="Q18" t="s">
         <v>185</v>
       </c>
-      <c r="R18">
-        <v>6</v>
+      <c r="R18" t="s">
+        <v>186</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2179,8 +2183,8 @@
       <c r="Q19" t="s">
         <v>173</v>
       </c>
-      <c r="R19">
-        <v>0</v>
+      <c r="R19" t="s">
+        <v>186</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>14</v>
@@ -2238,8 +2242,8 @@
       <c r="Q20" t="s">
         <v>173</v>
       </c>
-      <c r="R20">
-        <v>0</v>
+      <c r="R20" t="s">
+        <v>186</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>173</v>
@@ -2297,8 +2301,8 @@
       <c r="Q21" t="s">
         <v>173</v>
       </c>
-      <c r="R21">
-        <v>6</v>
+      <c r="R21" t="s">
+        <v>186</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>14</v>
@@ -2356,11 +2360,11 @@
       <c r="Q22" t="s">
         <v>173</v>
       </c>
-      <c r="R22">
-        <v>0</v>
+      <c r="R22" t="s">
+        <v>186</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2415,11 +2419,11 @@
       <c r="Q23" t="s">
         <v>173</v>
       </c>
-      <c r="R23">
-        <v>0</v>
+      <c r="R23" t="s">
+        <v>186</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2474,8 +2478,8 @@
       <c r="Q24" t="s">
         <v>173</v>
       </c>
-      <c r="R24">
-        <v>6</v>
+      <c r="R24" t="s">
+        <v>186</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>14</v>
@@ -2533,8 +2537,8 @@
       <c r="Q25" t="s">
         <v>173</v>
       </c>
-      <c r="R25">
-        <v>0</v>
+      <c r="R25" t="s">
+        <v>186</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>14</v>
@@ -2592,8 +2596,8 @@
       <c r="Q26" t="s">
         <v>173</v>
       </c>
-      <c r="R26">
-        <v>6</v>
+      <c r="R26" t="s">
+        <v>186</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>173</v>
@@ -2651,11 +2655,11 @@
       <c r="Q27" t="s">
         <v>173</v>
       </c>
-      <c r="R27">
-        <v>0</v>
+      <c r="R27" t="s">
+        <v>186</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2710,8 +2714,8 @@
       <c r="Q28" t="s">
         <v>173</v>
       </c>
-      <c r="R28">
-        <v>6.5</v>
+      <c r="R28" t="s">
+        <v>186</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>173</v>
@@ -2769,8 +2773,8 @@
       <c r="Q29" t="s">
         <v>173</v>
       </c>
-      <c r="R29">
-        <v>0</v>
+      <c r="R29" t="s">
+        <v>186</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>13</v>
@@ -2828,8 +2832,8 @@
       <c r="Q30" t="s">
         <v>183</v>
       </c>
-      <c r="R30">
-        <v>0</v>
+      <c r="R30" t="s">
+        <v>186</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>15</v>
@@ -2887,8 +2891,8 @@
       <c r="Q31" t="s">
         <v>173</v>
       </c>
-      <c r="R31">
-        <v>6.25</v>
+      <c r="R31" t="s">
+        <v>186</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>173</v>
@@ -2946,8 +2950,8 @@
       <c r="Q32" t="s">
         <v>173</v>
       </c>
-      <c r="R32">
-        <v>6</v>
+      <c r="R32" t="s">
+        <v>186</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>173</v>
@@ -3005,11 +3009,11 @@
       <c r="Q33" t="s">
         <v>173</v>
       </c>
-      <c r="R33">
-        <v>0</v>
+      <c r="R33" t="s">
+        <v>186</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -3064,11 +3068,11 @@
       <c r="Q34" t="s">
         <v>173</v>
       </c>
-      <c r="R34">
-        <v>2.75</v>
+      <c r="R34" t="s">
+        <v>186</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -3123,8 +3127,8 @@
       <c r="Q35" t="s">
         <v>173</v>
       </c>
-      <c r="R35">
-        <v>5.5</v>
+      <c r="R35" t="s">
+        <v>186</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>173</v>
@@ -3182,8 +3186,8 @@
       <c r="Q36" t="s">
         <v>180</v>
       </c>
-      <c r="R36">
-        <v>5.5</v>
+      <c r="R36" t="s">
+        <v>186</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>173</v>
@@ -3241,8 +3245,8 @@
       <c r="Q37" t="s">
         <v>180</v>
       </c>
-      <c r="R37">
-        <v>4</v>
+      <c r="R37" t="s">
+        <v>186</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>13</v>
@@ -3300,11 +3304,11 @@
       <c r="Q38" t="s">
         <v>173</v>
       </c>
-      <c r="R38">
-        <v>1.83</v>
+      <c r="R38" t="s">
+        <v>186</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3359,8 +3363,8 @@
       <c r="Q39" t="s">
         <v>173</v>
       </c>
-      <c r="R39">
-        <v>6.22</v>
+      <c r="R39" t="s">
+        <v>186</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>173</v>
@@ -3481,7 +3485,7 @@
         <v>4.5</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3599,7 +3603,7 @@
         <v>6.31</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3658,7 +3662,7 @@
         <v>7.19</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3717,7 +3721,7 @@
         <v>6.69</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3835,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3894,7 +3898,7 @@
         <v>5</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -4130,7 +4134,7 @@
         <v>1.06</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -4425,7 +4429,7 @@
         <v>6.12</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4661,7 +4665,7 @@
         <v>5.12</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4956,7 +4960,7 @@
         <v>3.88</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -5192,7 +5196,7 @@
         <v>5.25</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -5251,7 +5255,7 @@
         <v>2.56</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -5428,7 +5432,7 @@
         <v>1.38</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5546,7 +5550,7 @@
         <v>2.62</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -5664,7 +5668,7 @@
         <v>4.62</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -5723,7 +5727,7 @@
         <v>2.31</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -5782,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5959,7 +5963,7 @@
         <v>2.38</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -6018,7 +6022,7 @@
         <v>4.56</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -6313,7 +6317,7 @@
         <v>2.95</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -6667,7 +6671,7 @@
         <v>4.27</v>
       </c>
       <c r="S95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -6726,7 +6730,7 @@
         <v>3.18</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:19">
@@ -6844,7 +6848,7 @@
         <v>1.73</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:19">
@@ -7257,7 +7261,7 @@
         <v>1.14</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -7375,7 +7379,7 @@
         <v>3.95</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -7552,7 +7556,7 @@
         <v>3.68</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8083,7 +8087,7 @@
         <v>3.18</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -8260,7 +8264,7 @@
         <v>4.18</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -8496,7 +8500,7 @@
         <v>2.32</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -8555,7 +8559,7 @@
         <v>1.18</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -8673,7 +8677,7 @@
         <v>4.27</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9027,7 +9031,7 @@
         <v>4.41</v>
       </c>
       <c r="S135" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -9145,7 +9149,7 @@
         <v>1.27</v>
       </c>
       <c r="S137" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -9263,7 +9267,7 @@
         <v>2.41</v>
       </c>
       <c r="S139" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -9381,7 +9385,7 @@
         <v>2.82</v>
       </c>
       <c r="S141" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -9440,7 +9444,7 @@
         <v>3.91</v>
       </c>
       <c r="S142" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -9558,7 +9562,7 @@
         <v>2.27</v>
       </c>
       <c r="S144" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -9735,7 +9739,7 @@
         <v>2.95</v>
       </c>
       <c r="S147" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9794,7 +9798,7 @@
         <v>4.41</v>
       </c>
       <c r="S148" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -9912,7 +9916,7 @@
         <v>4</v>
       </c>
       <c r="S150" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -10089,7 +10093,7 @@
         <v>4.11</v>
       </c>
       <c r="S153" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -10148,7 +10152,7 @@
         <v>3.83</v>
       </c>
       <c r="S154" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -10207,7 +10211,7 @@
         <v>2.83</v>
       </c>
       <c r="S155" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
